--- a/COLOQUE_AQUI_CHECKLIST/checklist_equipamentos_CBO Isabella.xlsx
+++ b/COLOQUE_AQUI_CHECKLIST/checklist_equipamentos_CBO Isabella.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaomachado\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao\OneDrive\Desktop\AUTOMATIZADOR_LEVANTAMENTOS\COLOQUE_AQUI_CHECKLIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69FB59E2-2945-4EC6-A3C2-F0A485C7CE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947AD847-28E4-444C-AC00-704E474CC6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
   <si>
     <t>Item</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>Data:16/12/25</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>rack 12US X 570mm intelbras</t>
   </si>
 </sst>
 </file>
@@ -810,10 +816,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.21875" customWidth="1"/>
@@ -1780,6 +1786,23 @@
         <v>0</v>
       </c>
       <c r="E60" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="7" t="b">
         <v>0</v>
       </c>
     </row>
